--- a/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Triphammer_20251114.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,20 +454,14 @@
           <t>Cream Cheese</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>62.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>62.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>62</v>
+      </c>
+      <c r="E2" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Oat Milk</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>16.09</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>112.63</t>
-        </is>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="E3" t="n">
+        <v>112.63</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Almond Milk</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>35.74</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>107.22</t>
-        </is>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="E4" t="n">
+        <v>107.22</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Monin - Vanilla</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>35.21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>70.42</t>
-        </is>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="E5" t="n">
+        <v>70.42</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Joe Tea - Black Unsweetened</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21.95</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Joe Tea - Ginseng Green</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>43.90</t>
-        </is>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="E7" t="n">
+        <v>43.9</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Joe Tea - Half &amp; Half</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="E8" t="n">
+        <v>21.95</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Joe Tea - Lemon</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>43.90</t>
-        </is>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="E9" t="n">
+        <v>43.9</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>Mousse Cup - Chocolate</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="E10" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +643,56 @@
           <t>Roma - Tiramisu Plastic Cup</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>101.43</t>
-        </is>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="E11" t="n">
+        <v>101.43</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TN454</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Mango</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TN362</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Pineapple</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13.38</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Triphammer_20251114.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,6 +695,762 @@
         <v>13.38</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>K1570</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Buttermilk</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.59</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BR632</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cantaloupe - Fresh (Chunk)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="E15" t="n">
+        <v>161.96</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VR126</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cheddar - Extra Sharp White</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>25460</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hard Boiled Egg</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="E17" t="n">
+        <v>128.37</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FN108</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mango - Fresh (Chunk)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="E18" t="n">
+        <v>184.86</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BR628</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pineapple - Fresh (Chunk)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="E19" t="n">
+        <v>255.48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FT548</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Vinegar - Rice Seasoned</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HN732</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Avocado - Hand Scooped</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="E21" t="n">
+        <v>230.52</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L6434</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Barley</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>41.07</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LF010</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Base - Vegetable</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>144.75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10600</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Can - Great Northern Bean</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="E24" t="n">
+        <v>71.34</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CG686</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Chicken Breast - Retail (cooked)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="E25" t="n">
+        <v>473.76</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>V8852</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Chicken Filet - Breaded 4 oz (Raw)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="E26" t="n">
+        <v>274.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ABK40</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Chicken Wing - Fully Cooked</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>142.58</v>
+      </c>
+      <c r="E27" t="n">
+        <v>285.16</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WF580</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Corned Beef (Sliced)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="E28" t="n">
+        <v>265.04</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A0184</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Garlic Spread</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>46.97</v>
+      </c>
+      <c r="E29" t="n">
+        <v>46.97</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CK336</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pan Spray</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CV664</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pasta - Elbow</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="E31" t="n">
+        <v>25.43</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>E3556</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pastrami (Sliced)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="E32" t="n">
+        <v>199.35</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NJ502</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pepper Jack (Sliced)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="E33" t="n">
+        <v>212.12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GT276</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pita Chips - Bulk</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="E34" t="n">
+        <v>71.86</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RC608</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PKT Sour Cream</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.79</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T7146</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pork Butt (Bone In)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>85.40000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BL568</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pork Rib (St Louis Style)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>86.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36776</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Prosciutto</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="E38" t="n">
+        <v>62.48</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NH016</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Provolone (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="E39" t="n">
+        <v>103.32</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>25204</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rice - Long Grain (Parboiled)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>83632</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Roast Beef (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>126.08</v>
+      </c>
+      <c r="E41" t="n">
+        <v>630.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>38476</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Salami (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="E42" t="n">
+        <v>93.59999999999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>17486</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Salmon Filet Skinless</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>110.89</v>
+      </c>
+      <c r="E43" t="n">
+        <v>221.78</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AV906</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Swiss (Sliced)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="E44" t="n">
+        <v>113.76</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DT820</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Turkey (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="E45" t="n">
+        <v>493.92</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NG746</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Wrap - Garlic Herb (12')</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="E46" t="n">
+        <v>29.35</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NH166</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Lettuce - Arcadian Blend</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>92.59999999999999</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>L9126</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Lettuce - Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" t="n">
+        <v>56.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>280.05</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>G1084</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Pear - Fresh</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>53.79</v>
+      </c>
+      <c r="E49" t="n">
+        <v>53.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
